--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.89615714522803</v>
+        <v>6.645625536099555</v>
       </c>
       <c r="D2" t="n">
-        <v>25.57214324281139</v>
+        <v>4.15547327695685</v>
       </c>
       <c r="E2" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F2" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.71082652670519</v>
+        <v>5.965509310589594</v>
       </c>
       <c r="D3" t="n">
-        <v>18.47371477387827</v>
+        <v>3.00197865075522</v>
       </c>
       <c r="E3" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F3" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.9151586035965</v>
+        <v>5.348713273084431</v>
       </c>
       <c r="D4" t="n">
-        <v>35.40253888513368</v>
+        <v>5.752912568834224</v>
       </c>
       <c r="E4" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F4" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.86813631776976</v>
+        <v>6.803572151637586</v>
       </c>
       <c r="D5" t="n">
-        <v>9.037179933030838</v>
+        <v>1.468541739117511</v>
       </c>
       <c r="E5" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F5" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.61472553517978</v>
+        <v>4.487392899466715</v>
       </c>
       <c r="D6" t="n">
-        <v>29.30711060908403</v>
+        <v>4.762405473976155</v>
       </c>
       <c r="E6" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F6" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.77353452720416</v>
+        <v>5.975699360670677</v>
       </c>
       <c r="D7" t="n">
-        <v>41.69743973883901</v>
+        <v>6.775833957561339</v>
       </c>
       <c r="E7" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F7" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97832811914341</v>
+        <v>6.983978319360805</v>
       </c>
       <c r="D8" t="n">
-        <v>21.78135821261887</v>
+        <v>3.539470709550566</v>
       </c>
       <c r="E8" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F8" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.41946275677194</v>
+        <v>6.730662697975441</v>
       </c>
       <c r="D9" t="n">
-        <v>36.35854574308645</v>
+        <v>5.908263683251548</v>
       </c>
       <c r="E9" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F9" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.33122308593208</v>
+        <v>4.603823751463964</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59279285956946</v>
+        <v>5.458828839680038</v>
       </c>
       <c r="E10" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F10" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.84362435378363</v>
+        <v>6.962088957489841</v>
       </c>
       <c r="D11" t="n">
-        <v>37.58544401775602</v>
+        <v>6.107634652885353</v>
       </c>
       <c r="E11" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F11" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.41854435028105</v>
+        <v>5.75551345692067</v>
       </c>
       <c r="D12" t="n">
-        <v>39.99545411954919</v>
+        <v>6.499261294426743</v>
       </c>
       <c r="E12" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F12" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.77954619141141</v>
+        <v>6.139176256104354</v>
       </c>
       <c r="D13" t="n">
-        <v>32.64190958731756</v>
+        <v>5.304310307939103</v>
       </c>
       <c r="E13" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F13" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.80924335854651</v>
+        <v>4.519002045763808</v>
       </c>
       <c r="D14" t="n">
-        <v>27.54971062854736</v>
+        <v>4.476827977138946</v>
       </c>
       <c r="E14" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F14" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>34.32842346315105</v>
+        <v>5.578368812762046</v>
       </c>
       <c r="D15" t="n">
-        <v>34.49913726560565</v>
+        <v>5.606109805660919</v>
       </c>
       <c r="E15" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F15" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.08141674327408</v>
+        <v>6.025730220782037</v>
       </c>
       <c r="D16" t="n">
-        <v>35.44087436025446</v>
+        <v>5.75914208354135</v>
       </c>
       <c r="E16" t="n">
-        <v>5.138704408762777</v>
+        <v>0.8350394664239512</v>
       </c>
       <c r="F16" t="n">
-        <v>8.541031407093849</v>
+        <v>1.387917603652751</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
